--- a/data/trans_dic/P1801_2016_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1801_2016_2023-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,33; 54,06</t>
+          <t>44,58; 54,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,27; 58,36</t>
+          <t>49,27; 58,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,12; 63,6</t>
+          <t>53,17; 63,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57,66; 65,78</t>
+          <t>58,73; 66,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,68; 56,9</t>
+          <t>49,61; 56,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,22; 60,35</t>
+          <t>54,85; 60,98</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,72; 55,28</t>
+          <t>44,38; 55,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,2; 61,88</t>
+          <t>50,81; 60,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,74; 63,11</t>
+          <t>53,36; 62,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,93; 60,92</t>
+          <t>51,75; 60,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,37; 57,83</t>
+          <t>50,07; 57,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,51; 60,22</t>
+          <t>52,73; 58,91</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48,98; 57,7</t>
+          <t>48,61; 57,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,46; 88,54</t>
+          <t>47,29; 56,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,32; 70,82</t>
+          <t>55,98; 71,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,08; 63,92</t>
+          <t>51,41; 63,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,04; 59,84</t>
+          <t>51,74; 59,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,58; 86,44</t>
+          <t>49,6; 57,17</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,26; 51,2</t>
+          <t>44,93; 50,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,79; 53,54</t>
+          <t>46,03; 52,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,15; 58,45</t>
+          <t>50,9; 58,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,05; 83,34</t>
+          <t>55,59; 61,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,49; 53,02</t>
+          <t>48,38; 53,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,64; 70,52</t>
+          <t>50,82; 55,42</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,93; 49,33</t>
+          <t>41,52; 49,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,73; 52,73</t>
+          <t>39,3; 48,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,67; 59,02</t>
+          <t>51,57; 58,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,85; 58,32</t>
+          <t>54,34; 60,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,03; 53,67</t>
+          <t>48,14; 53,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,97; 54,19</t>
+          <t>49,09; 54,11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,45; 28,7</t>
+          <t>18,97; 28,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,94; 32,18</t>
+          <t>12,79; 27,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,79; 61,72</t>
+          <t>55,88; 61,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45,0; 51,9</t>
+          <t>44,08; 50,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48,56; 54,14</t>
+          <t>48,76; 54,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,57; 45,32</t>
+          <t>38,05; 44,53</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>52,13%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,91; 48,41</t>
+          <t>44,9; 48,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>48,69; 64,14</t>
+          <t>46,42; 50,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55,4; 58,84</t>
+          <t>55,48; 58,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53,39; 64,73</t>
+          <t>54,47; 57,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,77; 53,16</t>
+          <t>50,71; 53,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,15; 61,13</t>
+          <t>50,99; 53,43</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>271138</t>
+          <t>295659</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275280</t>
+          <t>305232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>546418</t>
+          <t>600891</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>190221; 231973</t>
+          <t>191295; 234566</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>248403; 294224</t>
+          <t>270737; 320824</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>184364; 220722</t>
+          <t>184522; 219271</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>257046; 293210</t>
+          <t>285820; 323886</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>385601; 441605</t>
+          <t>385083; 441138</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>515027; 573293</t>
+          <t>568281; 631834</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>259200</t>
+          <t>268131</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>215511</t>
+          <t>236791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>474711</t>
+          <t>504922</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>168690; 208537</t>
+          <t>167418; 207728</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>236066; 279839</t>
+          <t>245512; 290374</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>196349; 234932</t>
+          <t>198636; 233924</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>198339; 232643</t>
+          <t>218618; 254788</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>377510; 433471</t>
+          <t>375243; 432376</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>446293; 502290</t>
+          <t>477559; 533568</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>470049</t>
+          <t>244490</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95697</t>
+          <t>107964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>565746</t>
+          <t>352454</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>255648; 301161</t>
+          <t>253717; 301132</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>343856; 591707</t>
+          <t>223025; 268004</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93557; 117647</t>
+          <t>92993; 118278</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84937; 106294</t>
+          <t>96037; 119158</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>358037; 411688</t>
+          <t>356018; 410010</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>447116; 721396</t>
+          <t>326593; 376446</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>518011</t>
+          <t>553653</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>655395</t>
+          <t>504051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1173406</t>
+          <t>1057704</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>520321; 588632</t>
+          <t>516548; 585042</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>483696; 553483</t>
+          <t>520488; 593289</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>422473; 482756</t>
+          <t>420367; 479278</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>557584; 814499</t>
+          <t>477532; 529436</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>957865; 1047396</t>
+          <t>955660; 1049724</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1058730; 1418379</t>
+          <t>1011192; 1102647</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>225149</t>
+          <t>247687</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>431771</t>
+          <t>474652</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>656920</t>
+          <t>722340</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>254056; 306173</t>
+          <t>257737; 306176</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202443; 249835</t>
+          <t>222781; 275628</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>381451; 435689</t>
+          <t>380679; 434931</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>326494; 490124</t>
+          <t>451025; 498797</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>652647; 729403</t>
+          <t>654261; 726766</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>551577; 712163</t>
+          <t>685763; 755818</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52078</t>
+          <t>46537</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>366302</t>
+          <t>399375</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>418379</t>
+          <t>445912</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52966; 82419</t>
+          <t>54469; 82437</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33517; 77389</t>
+          <t>30345; 66383</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>603612; 667831</t>
+          <t>604676; 667504</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>342103; 394514</t>
+          <t>371631; 428604</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>664837; 741302</t>
+          <t>667632; 742526</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>385932; 453494</t>
+          <t>411019; 481046</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1795625</t>
+          <t>1656157</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2039955</t>
+          <t>2028065</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3835580</t>
+          <t>3684222</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1520488; 1639118</t>
+          <t>1520197; 1635309</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1642342; 2163322</t>
+          <t>1596604; 1726965</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1956487; 2078073</t>
+          <t>1959298; 2077113</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1907111; 2312098</t>
+          <t>1976256; 2082494</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3512040; 3677444</t>
+          <t>3507528; 3675336</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3621290; 4245117</t>
+          <t>3603539; 3775643</t>
         </is>
       </c>
     </row>
